--- a/FireShieldAI_Milestone_Submission_Updated.xlsx
+++ b/FireShieldAI_Milestone_Submission_Updated.xlsx
@@ -622,7 +622,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/FireShieldAI_Milestone_Submission_Updated.xlsx
+++ b/FireShieldAI_Milestone_Submission_Updated.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/FireShieldAI_Milestone_Submission_Updated.xlsx
+++ b/FireShieldAI_Milestone_Submission_Updated.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/FireShieldAI_Milestone_Submission_Updated.xlsx
+++ b/FireShieldAI_Milestone_Submission_Updated.xlsx
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/FireShieldAI_Milestone_Submission_Updated.xlsx
+++ b/FireShieldAI_Milestone_Submission_Updated.xlsx
@@ -790,7 +790,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/FireShieldAI_Milestone_Submission_Updated.xlsx
+++ b/FireShieldAI_Milestone_Submission_Updated.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>

--- a/FireShieldAI_Milestone_Submission_Updated.xlsx
+++ b/FireShieldAI_Milestone_Submission_Updated.xlsx
@@ -874,7 +874,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Planned</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
